--- a/win台机/GTG_青春小馆自动发布微头条/账号配置.xlsx
+++ b/win台机/GTG_青春小馆自动发布微头条/账号配置.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="18252" yWindow="2292" windowWidth="21036" windowHeight="12120" tabRatio="600" firstSheet="0" activeTab="7" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="18252" yWindow="2292" windowWidth="21036" windowHeight="12120" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="不首发" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,7 +13,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败列表" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="发文汇总" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="硬终止账号" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待补漏" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -7537,40 +7536,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>账号名</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>漏发数</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>文稿名</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>生成时间</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>